--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_23.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:M151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,905 +469,6780 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:52.141</t>
+          <t>2026-05-29 09:45:17.418</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779509147668</v>
+        <v>1780022716207</v>
       </c>
       <c r="C2" t="n">
-        <v>88370</v>
+        <v>83141</v>
       </c>
       <c r="D2" t="n">
-        <v>5464.77</v>
+        <v>176.3</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>1108</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>323.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="L2" t="n">
+        <v>119</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.328</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:52.142</t>
+          <t>2026-05-29 09:45:17.446</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779509147869</v>
+        <v>1780022716407</v>
       </c>
       <c r="C3" t="n">
-        <v>88583</v>
+        <v>82637</v>
       </c>
       <c r="D3" t="n">
-        <v>5404.53</v>
+        <v>-336.51</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F3" t="n">
-        <v>1108</v>
+        <v>400</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>323.88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1038</v>
+      </c>
+      <c r="L3" t="n">
+        <v>113</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:52.355</t>
+          <t>2026-05-29 09:45:17.448</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779509148071</v>
+        <v>1780022716607</v>
       </c>
       <c r="C4" t="n">
-        <v>88749</v>
+        <v>82487</v>
       </c>
       <c r="D4" t="n">
-        <v>5300.3</v>
+        <v>-469.69</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F4" t="n">
-        <v>1108</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>323.88</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>839</v>
+      </c>
+      <c r="L4" t="n">
+        <v>111</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.013</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:52.755</t>
+          <t>2026-05-29 09:45:17.809</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779509148272</v>
+        <v>1780022716826</v>
       </c>
       <c r="C5" t="n">
-        <v>88451</v>
+        <v>82750</v>
       </c>
       <c r="D5" t="n">
-        <v>4737.29</v>
+        <v>-183.2</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F5" t="n">
-        <v>1108</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>323.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K5" t="n">
+        <v>982</v>
+      </c>
+      <c r="L5" t="n">
+        <v>113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.608</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:53.040</t>
+          <t>2026-05-29 09:45:17.811</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779509148473</v>
+        <v>1780022717026</v>
       </c>
       <c r="C6" t="n">
-        <v>88658</v>
+        <v>82596</v>
       </c>
       <c r="D6" t="n">
-        <v>4707.42</v>
+        <v>-328.04</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>1108</v>
+        <v>839</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>311.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>784</v>
+      </c>
+      <c r="L6" t="n">
+        <v>106</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.471</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:53.040</t>
+          <t>2026-05-29 09:45:18.342</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779509148674</v>
+        <v>1780022717226</v>
       </c>
       <c r="C7" t="n">
-        <v>88920</v>
+        <v>82661</v>
       </c>
       <c r="D7" t="n">
-        <v>4734.05</v>
+        <v>-246.64</v>
       </c>
       <c r="E7" t="n">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="G7" t="n">
-        <v>128.69</v>
+        <v>311.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1114</v>
+      </c>
+      <c r="L7" t="n">
+        <v>110</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.769</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:53.041</t>
+          <t>2026-05-29 09:45:18.387</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779509148876</v>
+        <v>1780022717426</v>
       </c>
       <c r="C8" t="n">
-        <v>88761</v>
+        <v>82780</v>
       </c>
       <c r="D8" t="n">
-        <v>4338.35</v>
+        <v>-115.31</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="G8" t="n">
-        <v>128.69</v>
+        <v>311.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>960</v>
+      </c>
+      <c r="L8" t="n">
+        <v>105</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.977</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:53.767</t>
+          <t>2026-05-29 09:45:18.662</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779509149077</v>
+        <v>1780022717626</v>
       </c>
       <c r="C9" t="n">
-        <v>88948</v>
+        <v>82578</v>
       </c>
       <c r="D9" t="n">
-        <v>4308.43</v>
+        <v>-311.54</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F9" t="n">
-        <v>926</v>
+        <v>839</v>
       </c>
       <c r="G9" t="n">
-        <v>128.69</v>
+        <v>311.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1034</v>
+      </c>
+      <c r="L9" t="n">
+        <v>110</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.643</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.060</t>
+          <t>2026-05-29 09:45:18.663</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779509149278</v>
+        <v>1780022717826</v>
       </c>
       <c r="C10" t="n">
-        <v>89138</v>
+        <v>81991</v>
       </c>
       <c r="D10" t="n">
-        <v>4283.01</v>
+        <v>-882.97</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F10" t="n">
-        <v>926</v>
+        <v>640</v>
       </c>
       <c r="G10" t="n">
-        <v>128.69</v>
+        <v>176.36</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>836</v>
+      </c>
+      <c r="L10" t="n">
+        <v>105</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.112</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.065</t>
+          <t>2026-05-29 09:45:19.057</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779509149480</v>
+        <v>1780022718026</v>
       </c>
       <c r="C11" t="n">
-        <v>88654</v>
+        <v>83212</v>
       </c>
       <c r="D11" t="n">
-        <v>3584.86</v>
+        <v>382.18</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>926</v>
+        <v>640</v>
       </c>
       <c r="G11" t="n">
-        <v>128.69</v>
+        <v>176.36</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1029</v>
+      </c>
+      <c r="L11" t="n">
+        <v>115</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.241</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.066</t>
+          <t>2026-05-29 09:45:19.059</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779509149681</v>
+        <v>1780022718226</v>
       </c>
       <c r="C12" t="n">
-        <v>88307</v>
+        <v>82927</v>
       </c>
       <c r="D12" t="n">
-        <v>3058.62</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
-        <v>926</v>
+        <v>460</v>
       </c>
       <c r="G12" t="n">
-        <v>128.69</v>
+        <v>176.23</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>831</v>
+      </c>
+      <c r="L12" t="n">
+        <v>111</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.971</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.539</t>
+          <t>2026-05-29 09:45:19.480</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779509149882</v>
+        <v>1780022718445</v>
       </c>
       <c r="C13" t="n">
-        <v>88840</v>
+        <v>82781</v>
       </c>
       <c r="D13" t="n">
-        <v>3438.69</v>
+        <v>-71.83</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="F13" t="n">
-        <v>926</v>
+        <v>460</v>
       </c>
       <c r="G13" t="n">
-        <v>128.69</v>
+        <v>176.23</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1034</v>
+      </c>
+      <c r="L13" t="n">
+        <v>120</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.086</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.810</t>
+          <t>2026-05-29 09:45:19.482</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779509150084</v>
+        <v>1780022718645</v>
       </c>
       <c r="C14" t="n">
-        <v>88934</v>
+        <v>82762</v>
       </c>
       <c r="D14" t="n">
-        <v>3360.75</v>
+        <v>-87.23999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="F14" t="n">
-        <v>1429</v>
+        <v>460</v>
       </c>
       <c r="G14" t="n">
-        <v>254.68</v>
+        <v>176.23</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>836</v>
+      </c>
+      <c r="L14" t="n">
+        <v>111</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.278</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.812</t>
+          <t>2026-05-29 09:45:19.896</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779509150285</v>
+        <v>1780022718845</v>
       </c>
       <c r="C15" t="n">
-        <v>89015</v>
+        <v>82822</v>
       </c>
       <c r="D15" t="n">
-        <v>3273.71</v>
+        <v>-22.88</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="F15" t="n">
-        <v>1429</v>
+        <v>659</v>
       </c>
       <c r="G15" t="n">
-        <v>254.68</v>
+        <v>172.96</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L15" t="n">
+        <v>113</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.872</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:54.818</t>
+          <t>2026-05-29 09:45:19.965</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779509150486</v>
+        <v>1780022719045</v>
       </c>
       <c r="C16" t="n">
-        <v>88956</v>
+        <v>82663</v>
       </c>
       <c r="D16" t="n">
-        <v>3051.03</v>
+        <v>-180.73</v>
       </c>
       <c r="E16" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="F16" t="n">
-        <v>1429</v>
+        <v>659</v>
       </c>
       <c r="G16" t="n">
-        <v>254.68</v>
+        <v>172.96</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K16" t="n">
+        <v>917</v>
+      </c>
+      <c r="L16" t="n">
+        <v>104</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:55.075</t>
+          <t>2026-05-29 09:45:20.294</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779509150688</v>
+        <v>1780022719245</v>
       </c>
       <c r="C17" t="n">
-        <v>89096</v>
+        <v>83527</v>
       </c>
       <c r="D17" t="n">
-        <v>3038.48</v>
+        <v>692.3</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="F17" t="n">
-        <v>1429</v>
+        <v>659</v>
       </c>
       <c r="G17" t="n">
-        <v>254.68</v>
+        <v>172.96</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1048</v>
+      </c>
+      <c r="L17" t="n">
+        <v>110</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.627</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:55.097</t>
+          <t>2026-05-29 09:45:20.297</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779509150889</v>
+        <v>1780022719445</v>
       </c>
       <c r="C18" t="n">
-        <v>89295</v>
+        <v>82608</v>
       </c>
       <c r="D18" t="n">
-        <v>3085.55</v>
+        <v>-261.31</v>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="F18" t="n">
-        <v>1429</v>
+        <v>520</v>
       </c>
       <c r="G18" t="n">
-        <v>254.68</v>
+        <v>176.02</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K18" t="n">
+        <v>850</v>
+      </c>
+      <c r="L18" t="n">
+        <v>110</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.964</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:55.099</t>
+          <t>2026-05-29 09:45:20.886</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779509151090</v>
+        <v>1780022719645</v>
       </c>
       <c r="C19" t="n">
-        <v>88922</v>
+        <v>82655</v>
       </c>
       <c r="D19" t="n">
-        <v>2558.27</v>
+        <v>-201.25</v>
       </c>
       <c r="E19" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="F19" t="n">
-        <v>1429</v>
+        <v>520</v>
       </c>
       <c r="G19" t="n">
-        <v>254.68</v>
+        <v>176.02</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L19" t="n">
+        <v>119</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.217</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:55.957</t>
+          <t>2026-05-29 09:45:20.889</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779509151291</v>
+        <v>1780022719845</v>
       </c>
       <c r="C20" t="n">
-        <v>87287</v>
+        <v>82367</v>
       </c>
       <c r="D20" t="n">
-        <v>795.36</v>
+        <v>-479.18</v>
       </c>
       <c r="E20" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="F20" t="n">
-        <v>1429</v>
+        <v>520</v>
       </c>
       <c r="G20" t="n">
-        <v>254.68</v>
+        <v>176.02</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1042</v>
+      </c>
+      <c r="L20" t="n">
+        <v>121</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:56.245</t>
+          <t>2026-05-29 09:45:21.090</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779509151493</v>
+        <v>1780022720064</v>
       </c>
       <c r="C21" t="n">
-        <v>87648</v>
+        <v>82390</v>
       </c>
       <c r="D21" t="n">
-        <v>1116.59</v>
+        <v>-432.23</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="F21" t="n">
-        <v>1429</v>
+        <v>520</v>
       </c>
       <c r="G21" t="n">
-        <v>254.68</v>
+        <v>176.02</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L21" t="n">
+        <v>124</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.069</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:56.245</t>
+          <t>2026-05-29 09:45:21.403</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779509151694</v>
+        <v>1780022720264</v>
       </c>
       <c r="C22" t="n">
-        <v>88487</v>
+        <v>83939</v>
       </c>
       <c r="D22" t="n">
-        <v>1899.76</v>
+        <v>1138.39</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
-        <v>1429</v>
+        <v>520</v>
       </c>
       <c r="G22" t="n">
-        <v>254.68</v>
+        <v>176.02</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1138</v>
+      </c>
+      <c r="L22" t="n">
+        <v>107</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:56.251</t>
+          <t>2026-05-29 09:45:21.502</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779509151895</v>
+        <v>1780022720464</v>
       </c>
       <c r="C23" t="n">
-        <v>88381</v>
+        <v>83473</v>
       </c>
       <c r="D23" t="n">
-        <v>1698.78</v>
+        <v>615.47</v>
       </c>
       <c r="E23" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F23" t="n">
-        <v>1429</v>
+        <v>1019</v>
       </c>
       <c r="G23" t="n">
-        <v>254.68</v>
+        <v>204.02</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1037</v>
+      </c>
+      <c r="L23" t="n">
+        <v>122</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.193</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:56.508</t>
+          <t>2026-05-29 09:45:21.504</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779509152097</v>
+        <v>1780022720664</v>
       </c>
       <c r="C24" t="n">
-        <v>88175</v>
+        <v>83959</v>
       </c>
       <c r="D24" t="n">
-        <v>1407.84</v>
+        <v>1070.69</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F24" t="n">
-        <v>1429</v>
+        <v>1019</v>
       </c>
       <c r="G24" t="n">
-        <v>254.68</v>
+        <v>204.02</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>839</v>
+      </c>
+      <c r="L24" t="n">
+        <v>110</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.414</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:56.547</t>
+          <t>2026-05-29 09:45:22.314</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779509152298</v>
+        <v>1780022720864</v>
       </c>
       <c r="C25" t="n">
-        <v>87990</v>
+        <v>83535</v>
       </c>
       <c r="D25" t="n">
-        <v>1152.44</v>
+        <v>593.16</v>
       </c>
       <c r="E25" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F25" t="n">
-        <v>1429</v>
+        <v>1019</v>
       </c>
       <c r="G25" t="n">
-        <v>254.68</v>
+        <v>204.02</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1449</v>
+      </c>
+      <c r="L25" t="n">
+        <v>120</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.784</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:56.555</t>
+          <t>2026-05-29 09:45:22.329</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779509152499</v>
+        <v>1780022721064</v>
       </c>
       <c r="C26" t="n">
-        <v>88237</v>
+        <v>83712</v>
       </c>
       <c r="D26" t="n">
-        <v>1341.82</v>
+        <v>740.5</v>
       </c>
       <c r="E26" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F26" t="n">
-        <v>1429</v>
+        <v>1019</v>
       </c>
       <c r="G26" t="n">
-        <v>254.68</v>
+        <v>204.02</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1264</v>
+      </c>
+      <c r="L26" t="n">
+        <v>107</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.042</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:57.360</t>
+          <t>2026-05-29 09:45:22.511</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779509152701</v>
+        <v>1780022721264</v>
       </c>
       <c r="C27" t="n">
-        <v>88229</v>
+        <v>83940</v>
       </c>
       <c r="D27" t="n">
-        <v>1266.73</v>
+        <v>931.48</v>
       </c>
       <c r="E27" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="F27" t="n">
-        <v>2637</v>
+        <v>1019</v>
       </c>
       <c r="G27" t="n">
-        <v>254.68</v>
+        <v>204.02</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1246</v>
+      </c>
+      <c r="L27" t="n">
+        <v>109</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:57.610</t>
+          <t>2026-05-29 09:45:22.542</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779509152902</v>
+        <v>1780022721464</v>
       </c>
       <c r="C28" t="n">
-        <v>88400</v>
+        <v>82727</v>
       </c>
       <c r="D28" t="n">
-        <v>1374.39</v>
+        <v>-328.1</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>2637</v>
+        <v>1000</v>
       </c>
       <c r="G28" t="n">
-        <v>254.68</v>
+        <v>217.59</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1077</v>
+      </c>
+      <c r="L28" t="n">
+        <v>106</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:57.640</t>
+          <t>2026-05-29 09:45:22.544</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779509153103</v>
+        <v>1780022721683</v>
       </c>
       <c r="C29" t="n">
-        <v>87925</v>
+        <v>83247</v>
       </c>
       <c r="D29" t="n">
-        <v>830.67</v>
+        <v>208.31</v>
       </c>
       <c r="E29" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F29" t="n">
-        <v>2637</v>
+        <v>1000</v>
       </c>
       <c r="G29" t="n">
-        <v>254.68</v>
+        <v>217.59</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K29" t="n">
+        <v>859</v>
+      </c>
+      <c r="L29" t="n">
+        <v>117</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.295</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:57.641</t>
+          <t>2026-05-29 09:45:23.244</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779509153305</v>
+        <v>1780022721883</v>
       </c>
       <c r="C30" t="n">
-        <v>88113</v>
+        <v>82828</v>
       </c>
       <c r="D30" t="n">
-        <v>977.14</v>
+        <v>-221.11</v>
       </c>
       <c r="E30" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F30" t="n">
-        <v>2637</v>
+        <v>1000</v>
       </c>
       <c r="G30" t="n">
-        <v>254.68</v>
+        <v>217.59</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L30" t="n">
+        <v>122</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.736</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-23 11:05:57.896</t>
+          <t>2026-05-29 09:45:23.246</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779509153506</v>
+        <v>1780022722083</v>
       </c>
       <c r="C31" t="n">
-        <v>64491</v>
+        <v>82530</v>
       </c>
       <c r="D31" t="n">
-        <v>-22693.72</v>
+        <v>-508.05</v>
       </c>
       <c r="E31" t="n">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F31" t="n">
-        <v>2637</v>
+        <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>254.68</v>
+        <v>217.59</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L31" t="n">
+        <v>110</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.418</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:23.847</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1780022722284</v>
+      </c>
+      <c r="C32" t="n">
+        <v>82241</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-771.65</v>
+      </c>
+      <c r="E32" t="n">
+        <v>81</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1561</v>
+      </c>
+      <c r="L32" t="n">
+        <v>106</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.354</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:23.878</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1780022722483</v>
+      </c>
+      <c r="C33" t="n">
+        <v>82127</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-847.0700000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>81</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1393</v>
+      </c>
+      <c r="L33" t="n">
+        <v>107</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.368</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:23.904</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1780022722683</v>
+      </c>
+      <c r="C34" t="n">
+        <v>81886</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1045.71</v>
+      </c>
+      <c r="E34" t="n">
+        <v>81</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.818</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:23.906</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1780022722883</v>
+      </c>
+      <c r="C35" t="n">
+        <v>82036</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-843.4299999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>81</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L35" t="n">
+        <v>106</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.605</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:24.300</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1780022723083</v>
+      </c>
+      <c r="C36" t="n">
+        <v>82383</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-454.26</v>
+      </c>
+      <c r="E36" t="n">
+        <v>81</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1216</v>
+      </c>
+      <c r="L36" t="n">
+        <v>107</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.127</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:24.301</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1780022723302</v>
+      </c>
+      <c r="C37" t="n">
+        <v>81999</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-815.54</v>
+      </c>
+      <c r="E37" t="n">
+        <v>81</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G37" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J37" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K37" t="n">
+        <v>998</v>
+      </c>
+      <c r="L37" t="n">
+        <v>118</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:24.755</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1780022723502</v>
+      </c>
+      <c r="C38" t="n">
+        <v>82077</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-696.77</v>
+      </c>
+      <c r="E38" t="n">
+        <v>81</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G38" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1253</v>
+      </c>
+      <c r="L38" t="n">
+        <v>115</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.578</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:24.775</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1780022723702</v>
+      </c>
+      <c r="C39" t="n">
+        <v>82237</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-501.93</v>
+      </c>
+      <c r="E39" t="n">
+        <v>81</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1879</v>
+      </c>
+      <c r="G39" t="n">
+        <v>217.59</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1072</v>
+      </c>
+      <c r="L39" t="n">
+        <v>113</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:24.778</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1780022723902</v>
+      </c>
+      <c r="C40" t="n">
+        <v>82242</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-471.83</v>
+      </c>
+      <c r="E40" t="n">
+        <v>82</v>
+      </c>
+      <c r="F40" t="n">
+        <v>619</v>
+      </c>
+      <c r="G40" t="n">
+        <v>216.67</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K40" t="n">
+        <v>875</v>
+      </c>
+      <c r="L40" t="n">
+        <v>105</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.892</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:25.015</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1780022724102</v>
+      </c>
+      <c r="C41" t="n">
+        <v>82116</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-574.24</v>
+      </c>
+      <c r="E41" t="n">
+        <v>82</v>
+      </c>
+      <c r="F41" t="n">
+        <v>619</v>
+      </c>
+      <c r="G41" t="n">
+        <v>216.67</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K41" t="n">
+        <v>912</v>
+      </c>
+      <c r="L41" t="n">
+        <v>116</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.634</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:25.499</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1780022724302</v>
+      </c>
+      <c r="C42" t="n">
+        <v>82481</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-180.53</v>
+      </c>
+      <c r="E42" t="n">
+        <v>82</v>
+      </c>
+      <c r="F42" t="n">
+        <v>619</v>
+      </c>
+      <c r="G42" t="n">
+        <v>216.67</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L42" t="n">
+        <v>115</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.011</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:25.527</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1780022724502</v>
+      </c>
+      <c r="C43" t="n">
+        <v>82094</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-558.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>79</v>
+      </c>
+      <c r="F43" t="n">
+        <v>580</v>
+      </c>
+      <c r="G43" t="n">
+        <v>213.53</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J43" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1023</v>
+      </c>
+      <c r="L43" t="n">
+        <v>110</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.165</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:25.932</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1780022724702</v>
+      </c>
+      <c r="C44" t="n">
+        <v>82033</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-591.58</v>
+      </c>
+      <c r="E44" t="n">
+        <v>79</v>
+      </c>
+      <c r="F44" t="n">
+        <v>580</v>
+      </c>
+      <c r="G44" t="n">
+        <v>213.53</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1229</v>
+      </c>
+      <c r="L44" t="n">
+        <v>121</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.895</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:25.945</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1780022724921</v>
+      </c>
+      <c r="C45" t="n">
+        <v>82216</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-379</v>
+      </c>
+      <c r="E45" t="n">
+        <v>79</v>
+      </c>
+      <c r="F45" t="n">
+        <v>580</v>
+      </c>
+      <c r="G45" t="n">
+        <v>213.53</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1022</v>
+      </c>
+      <c r="L45" t="n">
+        <v>111</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.249</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:26.287</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1780022725121</v>
+      </c>
+      <c r="C46" t="n">
+        <v>82148</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-428.05</v>
+      </c>
+      <c r="E46" t="n">
+        <v>88</v>
+      </c>
+      <c r="F46" t="n">
+        <v>639</v>
+      </c>
+      <c r="G46" t="n">
+        <v>191.77</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L46" t="n">
+        <v>116</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.319</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:26.288</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1780022725321</v>
+      </c>
+      <c r="C47" t="n">
+        <v>81973</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-581.65</v>
+      </c>
+      <c r="E47" t="n">
+        <v>88</v>
+      </c>
+      <c r="F47" t="n">
+        <v>639</v>
+      </c>
+      <c r="G47" t="n">
+        <v>191.77</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>966</v>
+      </c>
+      <c r="L47" t="n">
+        <v>115</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:26.602</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1780022725521</v>
+      </c>
+      <c r="C48" t="n">
+        <v>82222</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-303.56</v>
+      </c>
+      <c r="E48" t="n">
+        <v>88</v>
+      </c>
+      <c r="F48" t="n">
+        <v>639</v>
+      </c>
+      <c r="G48" t="n">
+        <v>191.77</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L48" t="n">
+        <v>122</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1.287</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:26.604</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1780022725721</v>
+      </c>
+      <c r="C49" t="n">
+        <v>82343</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-167.39</v>
+      </c>
+      <c r="E49" t="n">
+        <v>97</v>
+      </c>
+      <c r="F49" t="n">
+        <v>620</v>
+      </c>
+      <c r="G49" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K49" t="n">
+        <v>881</v>
+      </c>
+      <c r="L49" t="n">
+        <v>115</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.782</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:27.145</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1780022725922</v>
+      </c>
+      <c r="C50" t="n">
+        <v>82337</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-165.02</v>
+      </c>
+      <c r="E50" t="n">
+        <v>97</v>
+      </c>
+      <c r="F50" t="n">
+        <v>620</v>
+      </c>
+      <c r="G50" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1222</v>
+      </c>
+      <c r="L50" t="n">
+        <v>108</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:27.147</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1780022726121</v>
+      </c>
+      <c r="C51" t="n">
+        <v>82377</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-116.77</v>
+      </c>
+      <c r="E51" t="n">
+        <v>97</v>
+      </c>
+      <c r="F51" t="n">
+        <v>620</v>
+      </c>
+      <c r="G51" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1026</v>
+      </c>
+      <c r="L51" t="n">
+        <v>110</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.822</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:27.160</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1780022726322</v>
+      </c>
+      <c r="C52" t="n">
+        <v>82224</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-263.93</v>
+      </c>
+      <c r="E52" t="n">
+        <v>97</v>
+      </c>
+      <c r="F52" t="n">
+        <v>620</v>
+      </c>
+      <c r="G52" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K52" t="n">
+        <v>836</v>
+      </c>
+      <c r="L52" t="n">
+        <v>104</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.331</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:27.484</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1780022726541</v>
+      </c>
+      <c r="C53" t="n">
+        <v>82172</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-302.73</v>
+      </c>
+      <c r="E53" t="n">
+        <v>97</v>
+      </c>
+      <c r="F53" t="n">
+        <v>620</v>
+      </c>
+      <c r="G53" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K53" t="n">
+        <v>942</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.123</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:27.854</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1780022726760</v>
+      </c>
+      <c r="C54" t="n">
+        <v>82182</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-277.59</v>
+      </c>
+      <c r="E54" t="n">
+        <v>97</v>
+      </c>
+      <c r="F54" t="n">
+        <v>620</v>
+      </c>
+      <c r="G54" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1093</v>
+      </c>
+      <c r="L54" t="n">
+        <v>124</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.984</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:27.902</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1780022726960</v>
+      </c>
+      <c r="C55" t="n">
+        <v>82352</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-93.70999999999999</v>
+      </c>
+      <c r="E55" t="n">
+        <v>97</v>
+      </c>
+      <c r="F55" t="n">
+        <v>620</v>
+      </c>
+      <c r="G55" t="n">
+        <v>186.24</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K55" t="n">
+        <v>940</v>
+      </c>
+      <c r="L55" t="n">
+        <v>113</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.698</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:28.306</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1780022727161</v>
+      </c>
+      <c r="C56" t="n">
+        <v>82439</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="E56" t="n">
+        <v>84</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G56" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1144</v>
+      </c>
+      <c r="L56" t="n">
+        <v>107</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.991</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:28.307</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1780022727360</v>
+      </c>
+      <c r="C57" t="n">
+        <v>82293</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-147.93</v>
+      </c>
+      <c r="E57" t="n">
+        <v>84</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G57" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K57" t="n">
+        <v>946</v>
+      </c>
+      <c r="L57" t="n">
+        <v>116</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.949</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.085</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1780022727561</v>
+      </c>
+      <c r="C58" t="n">
+        <v>82639</v>
+      </c>
+      <c r="D58" t="n">
+        <v>205.47</v>
+      </c>
+      <c r="E58" t="n">
+        <v>84</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G58" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1524</v>
+      </c>
+      <c r="L58" t="n">
+        <v>107</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.672</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.087</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1780022727761</v>
+      </c>
+      <c r="C59" t="n">
+        <v>82365</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-78.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>84</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G59" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L59" t="n">
+        <v>106</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.069</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.102</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1780022727961</v>
+      </c>
+      <c r="C60" t="n">
+        <v>82161</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-278.86</v>
+      </c>
+      <c r="E60" t="n">
+        <v>84</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G60" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1139</v>
+      </c>
+      <c r="L60" t="n">
+        <v>105</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.984</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.611</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1780022728160</v>
+      </c>
+      <c r="C61" t="n">
+        <v>82409</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-16.92</v>
+      </c>
+      <c r="E61" t="n">
+        <v>84</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G61" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1451</v>
+      </c>
+      <c r="L61" t="n">
+        <v>109</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.613</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1780022728379</v>
+      </c>
+      <c r="C62" t="n">
+        <v>82200</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-225.08</v>
+      </c>
+      <c r="E62" t="n">
+        <v>84</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G62" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1234</v>
+      </c>
+      <c r="L62" t="n">
+        <v>109</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.614</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1780022728579</v>
+      </c>
+      <c r="C63" t="n">
+        <v>81991</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-422.82</v>
+      </c>
+      <c r="E63" t="n">
+        <v>84</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G63" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L63" t="n">
+        <v>115</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.587</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:29.616</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1780022728780</v>
+      </c>
+      <c r="C64" t="n">
+        <v>82332</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-60.68</v>
+      </c>
+      <c r="E64" t="n">
+        <v>84</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G64" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K64" t="n">
+        <v>835</v>
+      </c>
+      <c r="L64" t="n">
+        <v>107</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.053</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:30.002</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1780022728999</v>
+      </c>
+      <c r="C65" t="n">
+        <v>82182</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-207.65</v>
+      </c>
+      <c r="E65" t="n">
+        <v>84</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1979</v>
+      </c>
+      <c r="G65" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1003</v>
+      </c>
+      <c r="L65" t="n">
+        <v>118</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.578</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:30.486</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1780022729200</v>
+      </c>
+      <c r="C66" t="n">
+        <v>81983</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-396.26</v>
+      </c>
+      <c r="E66" t="n">
+        <v>84</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1979</v>
+      </c>
+      <c r="G66" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1285</v>
+      </c>
+      <c r="L66" t="n">
+        <v>107</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.712</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:30.495</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1780022729399</v>
+      </c>
+      <c r="C67" t="n">
+        <v>82103</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-256.45</v>
+      </c>
+      <c r="E67" t="n">
+        <v>84</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1979</v>
+      </c>
+      <c r="G67" t="n">
+        <v>279.31</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L67" t="n">
+        <v>111</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1.109</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:30.497</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1780022729599</v>
+      </c>
+      <c r="C68" t="n">
+        <v>82302</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-44.63</v>
+      </c>
+      <c r="E68" t="n">
+        <v>81</v>
+      </c>
+      <c r="F68" t="n">
+        <v>640</v>
+      </c>
+      <c r="G68" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K68" t="n">
+        <v>896</v>
+      </c>
+      <c r="L68" t="n">
+        <v>106</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.773</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.042</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1780022729799</v>
+      </c>
+      <c r="C69" t="n">
+        <v>82101</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-243.4</v>
+      </c>
+      <c r="E69" t="n">
+        <v>81</v>
+      </c>
+      <c r="F69" t="n">
+        <v>640</v>
+      </c>
+      <c r="G69" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2242</v>
+      </c>
+      <c r="L69" t="n">
+        <v>108</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.661</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.043</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1780022730018</v>
+      </c>
+      <c r="C70" t="n">
+        <v>82604</v>
+      </c>
+      <c r="D70" t="n">
+        <v>271.77</v>
+      </c>
+      <c r="E70" t="n">
+        <v>81</v>
+      </c>
+      <c r="F70" t="n">
+        <v>640</v>
+      </c>
+      <c r="G70" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L70" t="n">
+        <v>107</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.044</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1780022730218</v>
+      </c>
+      <c r="C71" t="n">
+        <v>82405</v>
+      </c>
+      <c r="D71" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="E71" t="n">
+        <v>81</v>
+      </c>
+      <c r="F71" t="n">
+        <v>640</v>
+      </c>
+      <c r="G71" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1825</v>
+      </c>
+      <c r="L71" t="n">
+        <v>101</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.555</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.045</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1780022730419</v>
+      </c>
+      <c r="C72" t="n">
+        <v>82182</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-166.77</v>
+      </c>
+      <c r="E72" t="n">
+        <v>81</v>
+      </c>
+      <c r="F72" t="n">
+        <v>640</v>
+      </c>
+      <c r="G72" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1625</v>
+      </c>
+      <c r="L72" t="n">
+        <v>106</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.738</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.418</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1780022730638</v>
+      </c>
+      <c r="C73" t="n">
+        <v>82231</v>
+      </c>
+      <c r="D73" t="n">
+        <v>-109.44</v>
+      </c>
+      <c r="E73" t="n">
+        <v>81</v>
+      </c>
+      <c r="F73" t="n">
+        <v>640</v>
+      </c>
+      <c r="G73" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1779</v>
+      </c>
+      <c r="L73" t="n">
+        <v>110</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.897</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.419</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1780022730838</v>
+      </c>
+      <c r="C74" t="n">
+        <v>82168</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-166.96</v>
+      </c>
+      <c r="E74" t="n">
+        <v>81</v>
+      </c>
+      <c r="F74" t="n">
+        <v>640</v>
+      </c>
+      <c r="G74" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1580</v>
+      </c>
+      <c r="L74" t="n">
+        <v>107</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.845</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.420</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1780022731038</v>
+      </c>
+      <c r="C75" t="n">
+        <v>81886</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-440.62</v>
+      </c>
+      <c r="E75" t="n">
+        <v>81</v>
+      </c>
+      <c r="F75" t="n">
+        <v>640</v>
+      </c>
+      <c r="G75" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1381</v>
+      </c>
+      <c r="L75" t="n">
+        <v>106</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.129</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.422</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1780022731238</v>
+      </c>
+      <c r="C76" t="n">
+        <v>81896</v>
+      </c>
+      <c r="D76" t="n">
+        <v>-408.59</v>
+      </c>
+      <c r="E76" t="n">
+        <v>81</v>
+      </c>
+      <c r="F76" t="n">
+        <v>640</v>
+      </c>
+      <c r="G76" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1183</v>
+      </c>
+      <c r="L76" t="n">
+        <v>108</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.894</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.841</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1780022731438</v>
+      </c>
+      <c r="C77" t="n">
+        <v>81705</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-579.16</v>
+      </c>
+      <c r="E77" t="n">
+        <v>81</v>
+      </c>
+      <c r="F77" t="n">
+        <v>640</v>
+      </c>
+      <c r="G77" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1403</v>
+      </c>
+      <c r="L77" t="n">
+        <v>102</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.897</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1780022731657</v>
+      </c>
+      <c r="C78" t="n">
+        <v>81731</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-524.2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>81</v>
+      </c>
+      <c r="F78" t="n">
+        <v>640</v>
+      </c>
+      <c r="G78" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1239</v>
+      </c>
+      <c r="L78" t="n">
+        <v>113</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.172</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:32.899</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1780022731857</v>
+      </c>
+      <c r="C79" t="n">
+        <v>81299</v>
+      </c>
+      <c r="D79" t="n">
+        <v>-929.99</v>
+      </c>
+      <c r="E79" t="n">
+        <v>81</v>
+      </c>
+      <c r="F79" t="n">
+        <v>640</v>
+      </c>
+      <c r="G79" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1041</v>
+      </c>
+      <c r="L79" t="n">
+        <v>111</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:33.460</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1780022732059</v>
+      </c>
+      <c r="C80" t="n">
+        <v>81406</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-776.49</v>
+      </c>
+      <c r="E80" t="n">
+        <v>81</v>
+      </c>
+      <c r="F80" t="n">
+        <v>640</v>
+      </c>
+      <c r="G80" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="J80" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L80" t="n">
+        <v>152</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.732</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:33.490</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1780022732277</v>
+      </c>
+      <c r="C81" t="n">
+        <v>81720</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-423.66</v>
+      </c>
+      <c r="E81" t="n">
+        <v>81</v>
+      </c>
+      <c r="F81" t="n">
+        <v>640</v>
+      </c>
+      <c r="G81" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1211</v>
+      </c>
+      <c r="L81" t="n">
+        <v>111</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.599</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:33.674</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1780022732478</v>
+      </c>
+      <c r="C82" t="n">
+        <v>81597</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-525.48</v>
+      </c>
+      <c r="E82" t="n">
+        <v>81</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G82" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1194</v>
+      </c>
+      <c r="L82" t="n">
+        <v>108</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.417</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:33.675</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1780022732677</v>
+      </c>
+      <c r="C83" t="n">
+        <v>81779</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-317.21</v>
+      </c>
+      <c r="E83" t="n">
+        <v>81</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G83" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>997</v>
+      </c>
+      <c r="L83" t="n">
+        <v>114</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.098</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1780022732878</v>
+      </c>
+      <c r="C84" t="n">
+        <v>81897</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-183.35</v>
+      </c>
+      <c r="E84" t="n">
+        <v>81</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G84" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1219</v>
+      </c>
+      <c r="L84" t="n">
+        <v>149</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.615</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.128</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1780022733077</v>
+      </c>
+      <c r="C85" t="n">
+        <v>81487</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-584.1799999999999</v>
+      </c>
+      <c r="E85" t="n">
+        <v>81</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G85" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L85" t="n">
+        <v>120</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.732</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.486</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1780022733297</v>
+      </c>
+      <c r="C86" t="n">
+        <v>81393</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-648.97</v>
+      </c>
+      <c r="E86" t="n">
+        <v>81</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G86" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.49</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1188</v>
+      </c>
+      <c r="L86" t="n">
+        <v>107</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.889</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.504</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1780022733496</v>
+      </c>
+      <c r="C87" t="n">
+        <v>81704</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-305.52</v>
+      </c>
+      <c r="E87" t="n">
+        <v>81</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2758</v>
+      </c>
+      <c r="G87" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="J87" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1007</v>
+      </c>
+      <c r="L87" t="n">
+        <v>106</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1.061</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.887</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1780022733697</v>
+      </c>
+      <c r="C88" t="n">
+        <v>81707</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-287.25</v>
+      </c>
+      <c r="E88" t="n">
+        <v>69</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G88" t="n">
+        <v>306.4</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="J88" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1188</v>
+      </c>
+      <c r="L88" t="n">
+        <v>105</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.274</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.888</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1780022733896</v>
+      </c>
+      <c r="C89" t="n">
+        <v>81671</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-308.88</v>
+      </c>
+      <c r="E89" t="n">
+        <v>69</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G89" t="n">
+        <v>306.4</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="K89" t="n">
+        <v>991</v>
+      </c>
+      <c r="L89" t="n">
+        <v>126</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.726</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:34.889</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1780022734096</v>
+      </c>
+      <c r="C90" t="n">
+        <v>81687</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-277.44</v>
+      </c>
+      <c r="E90" t="n">
+        <v>69</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G90" t="n">
+        <v>306.4</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K90" t="n">
+        <v>792</v>
+      </c>
+      <c r="L90" t="n">
+        <v>96</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.246</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:35.343</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1780022734296</v>
+      </c>
+      <c r="C91" t="n">
+        <v>81619</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-331.57</v>
+      </c>
+      <c r="E91" t="n">
+        <v>69</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G91" t="n">
+        <v>306.4</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1045</v>
+      </c>
+      <c r="L91" t="n">
+        <v>115</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.407</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:35.345</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1780022734496</v>
+      </c>
+      <c r="C92" t="n">
+        <v>81289</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-644.99</v>
+      </c>
+      <c r="E92" t="n">
+        <v>66</v>
+      </c>
+      <c r="F92" t="n">
+        <v>720</v>
+      </c>
+      <c r="G92" t="n">
+        <v>290.35</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K92" t="n">
+        <v>848</v>
+      </c>
+      <c r="L92" t="n">
+        <v>104</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:35.667</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1780022734696</v>
+      </c>
+      <c r="C93" t="n">
+        <v>81431</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-470.74</v>
+      </c>
+      <c r="E93" t="n">
+        <v>66</v>
+      </c>
+      <c r="F93" t="n">
+        <v>720</v>
+      </c>
+      <c r="G93" t="n">
+        <v>290.35</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K93" t="n">
+        <v>969</v>
+      </c>
+      <c r="L93" t="n">
+        <v>110</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1.486</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:35.668</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1780022734915</v>
+      </c>
+      <c r="C94" t="n">
+        <v>81597</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-281.2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>66</v>
+      </c>
+      <c r="F94" t="n">
+        <v>720</v>
+      </c>
+      <c r="G94" t="n">
+        <v>290.35</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K94" t="n">
+        <v>753</v>
+      </c>
+      <c r="L94" t="n">
+        <v>108</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:36.043</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1780022735115</v>
+      </c>
+      <c r="C95" t="n">
+        <v>81441</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-423.14</v>
+      </c>
+      <c r="E95" t="n">
+        <v>79</v>
+      </c>
+      <c r="F95" t="n">
+        <v>619</v>
+      </c>
+      <c r="G95" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K95" t="n">
+        <v>927</v>
+      </c>
+      <c r="L95" t="n">
+        <v>113</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.769</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:36.044</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1780022735315</v>
+      </c>
+      <c r="C96" t="n">
+        <v>81371</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-471.99</v>
+      </c>
+      <c r="E96" t="n">
+        <v>79</v>
+      </c>
+      <c r="F96" t="n">
+        <v>619</v>
+      </c>
+      <c r="G96" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>728</v>
+      </c>
+      <c r="L96" t="n">
+        <v>104</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.671</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:36.590</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1780022735515</v>
+      </c>
+      <c r="C97" t="n">
+        <v>81413</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-406.39</v>
+      </c>
+      <c r="E97" t="n">
+        <v>79</v>
+      </c>
+      <c r="F97" t="n">
+        <v>619</v>
+      </c>
+      <c r="G97" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1074</v>
+      </c>
+      <c r="L97" t="n">
+        <v>110</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.614</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:36.601</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1780022735715</v>
+      </c>
+      <c r="C98" t="n">
+        <v>81073</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-726.0700000000001</v>
+      </c>
+      <c r="E98" t="n">
+        <v>79</v>
+      </c>
+      <c r="F98" t="n">
+        <v>619</v>
+      </c>
+      <c r="G98" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>885</v>
+      </c>
+      <c r="L98" t="n">
+        <v>105</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.726</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:37.075</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1780022735915</v>
+      </c>
+      <c r="C99" t="n">
+        <v>81226</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-536.76</v>
+      </c>
+      <c r="E99" t="n">
+        <v>79</v>
+      </c>
+      <c r="F99" t="n">
+        <v>619</v>
+      </c>
+      <c r="G99" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L99" t="n">
+        <v>114</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.951</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:37.078</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1780022736115</v>
+      </c>
+      <c r="C100" t="n">
+        <v>81368</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-367.93</v>
+      </c>
+      <c r="E100" t="n">
+        <v>79</v>
+      </c>
+      <c r="F100" t="n">
+        <v>619</v>
+      </c>
+      <c r="G100" t="n">
+        <v>291.34</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K100" t="n">
+        <v>961</v>
+      </c>
+      <c r="L100" t="n">
+        <v>115</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1.226</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:37.393</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1780022736315</v>
+      </c>
+      <c r="C101" t="n">
+        <v>81265</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-452.53</v>
+      </c>
+      <c r="E101" t="n">
+        <v>67</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G101" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1077</v>
+      </c>
+      <c r="L101" t="n">
+        <v>125</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:37.394</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1780022736534</v>
+      </c>
+      <c r="C102" t="n">
+        <v>81260</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-434.9</v>
+      </c>
+      <c r="E102" t="n">
+        <v>67</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G102" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K102" t="n">
+        <v>859</v>
+      </c>
+      <c r="L102" t="n">
+        <v>111</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.133</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:37.752</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1780022736734</v>
+      </c>
+      <c r="C103" t="n">
+        <v>81625</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-48.16</v>
+      </c>
+      <c r="E103" t="n">
+        <v>87</v>
+      </c>
+      <c r="F103" t="n">
+        <v>479</v>
+      </c>
+      <c r="G103" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1017</v>
+      </c>
+      <c r="L103" t="n">
+        <v>115</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1.193</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:37.754</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1780022736934</v>
+      </c>
+      <c r="C104" t="n">
+        <v>81338</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-332.75</v>
+      </c>
+      <c r="E104" t="n">
+        <v>87</v>
+      </c>
+      <c r="F104" t="n">
+        <v>479</v>
+      </c>
+      <c r="G104" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K104" t="n">
+        <v>818</v>
+      </c>
+      <c r="L104" t="n">
+        <v>106</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.027</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:38.576</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1780022737134</v>
+      </c>
+      <c r="C105" t="n">
+        <v>81037</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-617.11</v>
+      </c>
+      <c r="E105" t="n">
+        <v>87</v>
+      </c>
+      <c r="F105" t="n">
+        <v>479</v>
+      </c>
+      <c r="G105" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1442</v>
+      </c>
+      <c r="L105" t="n">
+        <v>114</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.793</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:38.631</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1780022737334</v>
+      </c>
+      <c r="C106" t="n">
+        <v>81006</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-617.26</v>
+      </c>
+      <c r="E106" t="n">
+        <v>87</v>
+      </c>
+      <c r="F106" t="n">
+        <v>479</v>
+      </c>
+      <c r="G106" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1296</v>
+      </c>
+      <c r="L106" t="n">
+        <v>103</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1.431</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.307</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1780022737534</v>
+      </c>
+      <c r="C107" t="n">
+        <v>81299</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-293.39</v>
+      </c>
+      <c r="E107" t="n">
+        <v>87</v>
+      </c>
+      <c r="F107" t="n">
+        <v>479</v>
+      </c>
+      <c r="G107" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J107" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1772</v>
+      </c>
+      <c r="L107" t="n">
+        <v>112</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1.015</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.309</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1780022737734</v>
+      </c>
+      <c r="C108" t="n">
+        <v>81136</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-441.72</v>
+      </c>
+      <c r="E108" t="n">
+        <v>82</v>
+      </c>
+      <c r="F108" t="n">
+        <v>940</v>
+      </c>
+      <c r="G108" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1574</v>
+      </c>
+      <c r="L108" t="n">
+        <v>106</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1.115</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.310</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1780022737934</v>
+      </c>
+      <c r="C109" t="n">
+        <v>81585</v>
+      </c>
+      <c r="D109" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="E109" t="n">
+        <v>121</v>
+      </c>
+      <c r="F109" t="n">
+        <v>240</v>
+      </c>
+      <c r="G109" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L109" t="n">
+        <v>106</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.141</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.311</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1780022738153</v>
+      </c>
+      <c r="C110" t="n">
+        <v>81049</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-508.11</v>
+      </c>
+      <c r="E110" t="n">
+        <v>121</v>
+      </c>
+      <c r="F110" t="n">
+        <v>240</v>
+      </c>
+      <c r="G110" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1157</v>
+      </c>
+      <c r="L110" t="n">
+        <v>108</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.743</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.861</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1780022738353</v>
+      </c>
+      <c r="C111" t="n">
+        <v>81246</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-285.7</v>
+      </c>
+      <c r="E111" t="n">
+        <v>121</v>
+      </c>
+      <c r="F111" t="n">
+        <v>240</v>
+      </c>
+      <c r="G111" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1507</v>
+      </c>
+      <c r="L111" t="n">
+        <v>108</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1.202</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.863</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1780022738553</v>
+      </c>
+      <c r="C112" t="n">
+        <v>81668</v>
+      </c>
+      <c r="D112" t="n">
+        <v>150.58</v>
+      </c>
+      <c r="E112" t="n">
+        <v>134</v>
+      </c>
+      <c r="F112" t="n">
+        <v>599</v>
+      </c>
+      <c r="G112" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J112" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1309</v>
+      </c>
+      <c r="L112" t="n">
+        <v>119</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.211</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:39.907</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1780022738753</v>
+      </c>
+      <c r="C113" t="n">
+        <v>81333</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-191.94</v>
+      </c>
+      <c r="E113" t="n">
+        <v>134</v>
+      </c>
+      <c r="F113" t="n">
+        <v>599</v>
+      </c>
+      <c r="G113" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J113" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1152</v>
+      </c>
+      <c r="L113" t="n">
+        <v>121</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.993</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:40.777</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1780022738953</v>
+      </c>
+      <c r="C114" t="n">
+        <v>81208</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-307.35</v>
+      </c>
+      <c r="E114" t="n">
+        <v>134</v>
+      </c>
+      <c r="F114" t="n">
+        <v>599</v>
+      </c>
+      <c r="G114" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J114" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1822</v>
+      </c>
+      <c r="L114" t="n">
+        <v>120</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.889</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:40.778</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1780022739153</v>
+      </c>
+      <c r="C115" t="n">
+        <v>81286</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-213.98</v>
+      </c>
+      <c r="E115" t="n">
+        <v>134</v>
+      </c>
+      <c r="F115" t="n">
+        <v>599</v>
+      </c>
+      <c r="G115" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1624</v>
+      </c>
+      <c r="L115" t="n">
+        <v>107</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.319</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:40.791</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1780022739353</v>
+      </c>
+      <c r="C116" t="n">
+        <v>81157</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-332.28</v>
+      </c>
+      <c r="E116" t="n">
+        <v>134</v>
+      </c>
+      <c r="F116" t="n">
+        <v>599</v>
+      </c>
+      <c r="G116" t="n">
+        <v>378.59</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L116" t="n">
+        <v>108</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.085</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:40.796</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1780022739553</v>
+      </c>
+      <c r="C117" t="n">
+        <v>81241</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-231.67</v>
+      </c>
+      <c r="E117" t="n">
+        <v>120</v>
+      </c>
+      <c r="F117" t="n">
+        <v>880</v>
+      </c>
+      <c r="G117" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1242</v>
+      </c>
+      <c r="L117" t="n">
+        <v>110</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.728</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:40.937</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1780022739772</v>
+      </c>
+      <c r="C118" t="n">
+        <v>81522</v>
+      </c>
+      <c r="D118" t="n">
+        <v>60.92</v>
+      </c>
+      <c r="E118" t="n">
+        <v>120</v>
+      </c>
+      <c r="F118" t="n">
+        <v>880</v>
+      </c>
+      <c r="G118" t="n">
+        <v>332.86</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>1164</v>
+      </c>
+      <c r="L118" t="n">
+        <v>109</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.135</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:41.040</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1780022739972</v>
+      </c>
+      <c r="C119" t="n">
+        <v>81426</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-38.13</v>
+      </c>
+      <c r="E119" t="n">
+        <v>142</v>
+      </c>
+      <c r="F119" t="n">
+        <v>399</v>
+      </c>
+      <c r="G119" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J119" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1066</v>
+      </c>
+      <c r="L119" t="n">
+        <v>114</v>
+      </c>
+      <c r="M119" t="n">
+        <v>1.546</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:41.558</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1780022740172</v>
+      </c>
+      <c r="C120" t="n">
+        <v>81528</v>
+      </c>
+      <c r="D120" t="n">
+        <v>65.78</v>
+      </c>
+      <c r="E120" t="n">
+        <v>142</v>
+      </c>
+      <c r="F120" t="n">
+        <v>399</v>
+      </c>
+      <c r="G120" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J120" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1384</v>
+      </c>
+      <c r="L120" t="n">
+        <v>119</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.638</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:41.560</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1780022740372</v>
+      </c>
+      <c r="C121" t="n">
+        <v>81748</v>
+      </c>
+      <c r="D121" t="n">
+        <v>282.49</v>
+      </c>
+      <c r="E121" t="n">
+        <v>142</v>
+      </c>
+      <c r="F121" t="n">
+        <v>399</v>
+      </c>
+      <c r="G121" t="n">
+        <v>351.33</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1187</v>
+      </c>
+      <c r="L121" t="n">
+        <v>121</v>
+      </c>
+      <c r="M121" t="n">
+        <v>1.073</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:41.573</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1780022740572</v>
+      </c>
+      <c r="C122" t="n">
+        <v>81622</v>
+      </c>
+      <c r="D122" t="n">
+        <v>142.36</v>
+      </c>
+      <c r="E122" t="n">
+        <v>104</v>
+      </c>
+      <c r="F122" t="n">
+        <v>600</v>
+      </c>
+      <c r="G122" t="n">
+        <v>297.89</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L122" t="n">
+        <v>117</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.896</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:42.059</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1780022740772</v>
+      </c>
+      <c r="C123" t="n">
+        <v>81110</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-376.75</v>
+      </c>
+      <c r="E123" t="n">
+        <v>104</v>
+      </c>
+      <c r="F123" t="n">
+        <v>600</v>
+      </c>
+      <c r="G123" t="n">
+        <v>297.89</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1286</v>
+      </c>
+      <c r="L123" t="n">
+        <v>120</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.887</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:42.090</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1780022740972</v>
+      </c>
+      <c r="C124" t="n">
+        <v>81063</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-404.92</v>
+      </c>
+      <c r="E124" t="n">
+        <v>104</v>
+      </c>
+      <c r="F124" t="n">
+        <v>600</v>
+      </c>
+      <c r="G124" t="n">
+        <v>297.89</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1118</v>
+      </c>
+      <c r="L124" t="n">
+        <v>111</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.462</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.315</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1780022741172</v>
+      </c>
+      <c r="C125" t="n">
+        <v>81082</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-365.67</v>
+      </c>
+      <c r="E125" t="n">
+        <v>104</v>
+      </c>
+      <c r="F125" t="n">
+        <v>600</v>
+      </c>
+      <c r="G125" t="n">
+        <v>297.89</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K125" t="n">
+        <v>2141</v>
+      </c>
+      <c r="L125" t="n">
+        <v>119</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.359</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.361</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1780022741391</v>
+      </c>
+      <c r="C126" t="n">
+        <v>81032</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-397.39</v>
+      </c>
+      <c r="E126" t="n">
+        <v>104</v>
+      </c>
+      <c r="F126" t="n">
+        <v>600</v>
+      </c>
+      <c r="G126" t="n">
+        <v>297.89</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1968</v>
+      </c>
+      <c r="L126" t="n">
+        <v>107</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.162</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.362</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1780022741591</v>
+      </c>
+      <c r="C127" t="n">
+        <v>81490</v>
+      </c>
+      <c r="D127" t="n">
+        <v>80.48</v>
+      </c>
+      <c r="E127" t="n">
+        <v>93</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G127" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1770</v>
+      </c>
+      <c r="L127" t="n">
+        <v>118</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.021</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.363</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1780022741791</v>
+      </c>
+      <c r="C128" t="n">
+        <v>82151</v>
+      </c>
+      <c r="D128" t="n">
+        <v>737.46</v>
+      </c>
+      <c r="E128" t="n">
+        <v>93</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G128" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1572</v>
+      </c>
+      <c r="L128" t="n">
+        <v>122</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.711</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.373</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1780022741991</v>
+      </c>
+      <c r="C129" t="n">
+        <v>81958</v>
+      </c>
+      <c r="D129" t="n">
+        <v>507.58</v>
+      </c>
+      <c r="E129" t="n">
+        <v>93</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G129" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1381</v>
+      </c>
+      <c r="L129" t="n">
+        <v>108</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.719</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.392</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1780022742191</v>
+      </c>
+      <c r="C130" t="n">
+        <v>81535</v>
+      </c>
+      <c r="D130" t="n">
+        <v>59.21</v>
+      </c>
+      <c r="E130" t="n">
+        <v>93</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G130" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L130" t="n">
+        <v>110</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.845</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.429</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1780022742391</v>
+      </c>
+      <c r="C131" t="n">
+        <v>81707</v>
+      </c>
+      <c r="D131" t="n">
+        <v>228.25</v>
+      </c>
+      <c r="E131" t="n">
+        <v>93</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G131" t="n">
+        <v>319.47</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1037</v>
+      </c>
+      <c r="L131" t="n">
+        <v>108</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.954</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.654</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1780022742591</v>
+      </c>
+      <c r="C132" t="n">
+        <v>81932</v>
+      </c>
+      <c r="D132" t="n">
+        <v>441.83</v>
+      </c>
+      <c r="E132" t="n">
+        <v>89</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G132" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1062</v>
+      </c>
+      <c r="L132" t="n">
+        <v>118</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.849</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:43.670</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1780022742791</v>
+      </c>
+      <c r="C133" t="n">
+        <v>80860</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-652.26</v>
+      </c>
+      <c r="E133" t="n">
+        <v>89</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G133" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J133" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K133" t="n">
+        <v>878</v>
+      </c>
+      <c r="L133" t="n">
+        <v>119</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1.143</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:44.090</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1780022743010</v>
+      </c>
+      <c r="C134" t="n">
+        <v>81739</v>
+      </c>
+      <c r="D134" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="E134" t="n">
+        <v>89</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1140</v>
+      </c>
+      <c r="G134" t="n">
+        <v>344.91</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L134" t="n">
+        <v>116</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.884</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:44.092</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1780022743210</v>
+      </c>
+      <c r="C135" t="n">
+        <v>81350</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-142.61</v>
+      </c>
+      <c r="E135" t="n">
+        <v>78</v>
+      </c>
+      <c r="F135" t="n">
+        <v>579</v>
+      </c>
+      <c r="G135" t="n">
+        <v>295.01</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K135" t="n">
+        <v>880</v>
+      </c>
+      <c r="L135" t="n">
+        <v>104</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.411</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.152</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1780022743410</v>
+      </c>
+      <c r="C136" t="n">
+        <v>81540</v>
+      </c>
+      <c r="D136" t="n">
+        <v>54.52</v>
+      </c>
+      <c r="E136" t="n">
+        <v>78</v>
+      </c>
+      <c r="F136" t="n">
+        <v>579</v>
+      </c>
+      <c r="G136" t="n">
+        <v>295.01</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1742</v>
+      </c>
+      <c r="L136" t="n">
+        <v>109</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.645</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.154</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1780022743610</v>
+      </c>
+      <c r="C137" t="n">
+        <v>81768</v>
+      </c>
+      <c r="D137" t="n">
+        <v>279.79</v>
+      </c>
+      <c r="E137" t="n">
+        <v>88</v>
+      </c>
+      <c r="F137" t="n">
+        <v>420</v>
+      </c>
+      <c r="G137" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1543</v>
+      </c>
+      <c r="L137" t="n">
+        <v>116</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.615</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.443</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1780022743810</v>
+      </c>
+      <c r="C138" t="n">
+        <v>82012</v>
+      </c>
+      <c r="D138" t="n">
+        <v>509.8</v>
+      </c>
+      <c r="E138" t="n">
+        <v>88</v>
+      </c>
+      <c r="F138" t="n">
+        <v>420</v>
+      </c>
+      <c r="G138" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1632</v>
+      </c>
+      <c r="L138" t="n">
+        <v>110</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1.308</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.458</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1780022744010</v>
+      </c>
+      <c r="C139" t="n">
+        <v>82055</v>
+      </c>
+      <c r="D139" t="n">
+        <v>527.3099999999999</v>
+      </c>
+      <c r="E139" t="n">
+        <v>88</v>
+      </c>
+      <c r="F139" t="n">
+        <v>420</v>
+      </c>
+      <c r="G139" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1447</v>
+      </c>
+      <c r="L139" t="n">
+        <v>104</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.465</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1780022744210</v>
+      </c>
+      <c r="C140" t="n">
+        <v>82432</v>
+      </c>
+      <c r="D140" t="n">
+        <v>877.95</v>
+      </c>
+      <c r="E140" t="n">
+        <v>88</v>
+      </c>
+      <c r="F140" t="n">
+        <v>420</v>
+      </c>
+      <c r="G140" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1255</v>
+      </c>
+      <c r="L140" t="n">
+        <v>113</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.656</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.475</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1780022744410</v>
+      </c>
+      <c r="C141" t="n">
+        <v>82710</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1112.05</v>
+      </c>
+      <c r="E141" t="n">
+        <v>88</v>
+      </c>
+      <c r="F141" t="n">
+        <v>420</v>
+      </c>
+      <c r="G141" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1064</v>
+      </c>
+      <c r="L141" t="n">
+        <v>116</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.058</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.785</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1780022744629</v>
+      </c>
+      <c r="C142" t="n">
+        <v>82595</v>
+      </c>
+      <c r="D142" t="n">
+        <v>941.45</v>
+      </c>
+      <c r="E142" t="n">
+        <v>88</v>
+      </c>
+      <c r="F142" t="n">
+        <v>420</v>
+      </c>
+      <c r="G142" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1155</v>
+      </c>
+      <c r="L142" t="n">
+        <v>107</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.766</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:45.793</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1780022744829</v>
+      </c>
+      <c r="C143" t="n">
+        <v>82594</v>
+      </c>
+      <c r="D143" t="n">
+        <v>893.37</v>
+      </c>
+      <c r="E143" t="n">
+        <v>88</v>
+      </c>
+      <c r="F143" t="n">
+        <v>420</v>
+      </c>
+      <c r="G143" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>116</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.538</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:46.391</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1780022745029</v>
+      </c>
+      <c r="C144" t="n">
+        <v>82757</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1011.71</v>
+      </c>
+      <c r="E144" t="n">
+        <v>88</v>
+      </c>
+      <c r="F144" t="n">
+        <v>420</v>
+      </c>
+      <c r="G144" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.37</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1361</v>
+      </c>
+      <c r="L144" t="n">
+        <v>113</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.971</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:46.397</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1780022745229</v>
+      </c>
+      <c r="C145" t="n">
+        <v>82604</v>
+      </c>
+      <c r="D145" t="n">
+        <v>808.12</v>
+      </c>
+      <c r="E145" t="n">
+        <v>88</v>
+      </c>
+      <c r="F145" t="n">
+        <v>420</v>
+      </c>
+      <c r="G145" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1167</v>
+      </c>
+      <c r="L145" t="n">
+        <v>112</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.643</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:46.404</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1780022745429</v>
+      </c>
+      <c r="C146" t="n">
+        <v>82625</v>
+      </c>
+      <c r="D146" t="n">
+        <v>788.71</v>
+      </c>
+      <c r="E146" t="n">
+        <v>88</v>
+      </c>
+      <c r="F146" t="n">
+        <v>420</v>
+      </c>
+      <c r="G146" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J146" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K146" t="n">
+        <v>974</v>
+      </c>
+      <c r="L146" t="n">
+        <v>105</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1.094</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:46.792</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1780022745629</v>
+      </c>
+      <c r="C147" t="n">
+        <v>82562</v>
+      </c>
+      <c r="D147" t="n">
+        <v>686.28</v>
+      </c>
+      <c r="E147" t="n">
+        <v>88</v>
+      </c>
+      <c r="F147" t="n">
+        <v>420</v>
+      </c>
+      <c r="G147" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J147" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1162</v>
+      </c>
+      <c r="L147" t="n">
+        <v>113</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.995</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:46.793</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1780022745829</v>
+      </c>
+      <c r="C148" t="n">
+        <v>82728</v>
+      </c>
+      <c r="D148" t="n">
+        <v>817.96</v>
+      </c>
+      <c r="E148" t="n">
+        <v>88</v>
+      </c>
+      <c r="F148" t="n">
+        <v>420</v>
+      </c>
+      <c r="G148" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J148" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K148" t="n">
+        <v>964</v>
+      </c>
+      <c r="L148" t="n">
+        <v>116</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0.877</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:47.105</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1780022746048</v>
+      </c>
+      <c r="C149" t="n">
+        <v>82617</v>
+      </c>
+      <c r="D149" t="n">
+        <v>666.0700000000001</v>
+      </c>
+      <c r="E149" t="n">
+        <v>88</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2299</v>
+      </c>
+      <c r="G149" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="J149" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1056</v>
+      </c>
+      <c r="L149" t="n">
+        <v>111</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1.275</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:47.118</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1780022746248</v>
+      </c>
+      <c r="C150" t="n">
+        <v>82414</v>
+      </c>
+      <c r="D150" t="n">
+        <v>429.76</v>
+      </c>
+      <c r="E150" t="n">
+        <v>88</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2299</v>
+      </c>
+      <c r="G150" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J150" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K150" t="n">
+        <v>869</v>
+      </c>
+      <c r="L150" t="n">
+        <v>111</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:45:47.511</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1780022746449</v>
+      </c>
+      <c r="C151" t="n">
+        <v>82519</v>
+      </c>
+      <c r="D151" t="n">
+        <v>513.27</v>
+      </c>
+      <c r="E151" t="n">
+        <v>88</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2299</v>
+      </c>
+      <c r="G151" t="n">
+        <v>300.24</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Good (100%)</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1061</v>
+      </c>
+      <c r="L151" t="n">
+        <v>109</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
